--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -2214,32 +2214,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140344</v>
+        <v>130140312</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>97702</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633720</v>
+        <v>633608</v>
       </c>
       <c r="R17" t="n">
-        <v>6658686</v>
+        <v>6658722</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2285,11 +2285,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,7 +2311,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140339</v>
+        <v>130140344</v>
       </c>
       <c r="B18" t="n">
         <v>98831</v>
@@ -2351,10 +2346,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633700</v>
+        <v>633720</v>
       </c>
       <c r="R18" t="n">
-        <v>6658589</v>
+        <v>6658686</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2391,7 +2386,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10 buketter 1310</t>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2418,32 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130140312</v>
+        <v>130140339</v>
       </c>
       <c r="B19" t="n">
-        <v>97702</v>
+        <v>98831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633608</v>
+        <v>633700</v>
       </c>
       <c r="R19" t="n">
-        <v>6658722</v>
+        <v>6658589</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2489,6 +2484,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10 buketter 1310</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>130140331</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>130140320</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130140318</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>130140309</v>
       </c>
       <c r="B7" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>130140296</v>
       </c>
       <c r="B8" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>130140327</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>130140329</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>130140325</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>130140340</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>130140292</v>
       </c>
       <c r="B14" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>130140315</v>
       </c>
       <c r="B15" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>130140343</v>
       </c>
       <c r="B16" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,32 +2214,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140312</v>
+        <v>130140344</v>
       </c>
       <c r="B17" t="n">
-        <v>97702</v>
+        <v>98833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633608</v>
+        <v>633720</v>
       </c>
       <c r="R17" t="n">
-        <v>6658722</v>
+        <v>6658686</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2285,6 +2285,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2311,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140344</v>
+        <v>130140339</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633720</v>
+        <v>633700</v>
       </c>
       <c r="R18" t="n">
-        <v>6658686</v>
+        <v>6658589</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2386,7 +2391,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bukett 1301</t>
+          <t>10 buketter 1310</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,32 +2418,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130140339</v>
+        <v>130140312</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>97704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2448,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633700</v>
+        <v>633608</v>
       </c>
       <c r="R19" t="n">
-        <v>6658589</v>
+        <v>6658722</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2484,11 +2489,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10 buketter 1310</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,7 +2518,7 @@
         <v>130140336</v>
       </c>
       <c r="B20" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>130140322</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,7 +916,7 @@
         <v>130140331</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>130140320</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130140318</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>130140309</v>
       </c>
       <c r="B7" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>130140296</v>
       </c>
       <c r="B8" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>130140327</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>130140329</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>130140325</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>130140298</v>
       </c>
       <c r="B12" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>130140340</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,32 +1918,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140292</v>
+        <v>130140343</v>
       </c>
       <c r="B14" t="n">
-        <v>97079</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633626</v>
+        <v>633719</v>
       </c>
       <c r="R14" t="n">
-        <v>6658697</v>
+        <v>6658699</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,6 +1989,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2018,7 +2023,7 @@
         <v>130140315</v>
       </c>
       <c r="B15" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,32 +2117,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130140343</v>
+        <v>130140292</v>
       </c>
       <c r="B16" t="n">
-        <v>98833</v>
+        <v>97166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633719</v>
+        <v>633626</v>
       </c>
       <c r="R16" t="n">
-        <v>6658699</v>
+        <v>6658697</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2183,11 +2188,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2217,7 +2217,7 @@
         <v>130140344</v>
       </c>
       <c r="B17" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>130140339</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>130140312</v>
       </c>
       <c r="B19" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>130140336</v>
       </c>
       <c r="B20" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>130140322</v>
       </c>
       <c r="B21" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>130140303</v>
       </c>
       <c r="B22" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>130140307</v>
       </c>
       <c r="B23" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,6 +2910,404 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130294382</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gölinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>633614</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6658718</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>6 buketter</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130294380</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gölinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>633664</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6658700</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130294381</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gölinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>633661</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6658817</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130294384</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gölinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>633647</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6658734</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -1937,32 +1937,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140292</v>
+        <v>130140343</v>
       </c>
       <c r="B14" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633626</v>
+        <v>633719</v>
       </c>
       <c r="R14" t="n">
-        <v>6658697</v>
+        <v>6658699</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2008,6 +2008,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2034,32 +2039,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130140343</v>
+        <v>130140315</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>97791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633719</v>
+        <v>633550</v>
       </c>
       <c r="R15" t="n">
-        <v>6658699</v>
+        <v>6658729</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2105,11 +2110,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2136,32 +2136,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130140315</v>
+        <v>130140292</v>
       </c>
       <c r="B16" t="n">
-        <v>97791</v>
+        <v>97166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633550</v>
+        <v>633626</v>
       </c>
       <c r="R16" t="n">
-        <v>6658729</v>
+        <v>6658697</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B31" t="n">
         <v>98920</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R31" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,12 +3772,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3792,19 +3787,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B32" t="n">
         <v>98920</v>
@@ -3834,7 +3829,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3848,10 +3843,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R32" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3893,7 +3888,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4283,42 +4283,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130344259</v>
+        <v>130344254</v>
       </c>
       <c r="B36" t="n">
-        <v>98920</v>
+        <v>57823</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4327,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633692</v>
+        <v>633695</v>
       </c>
       <c r="R36" t="n">
-        <v>6658641</v>
+        <v>6658733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4362,7 +4358,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4372,12 +4368,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4404,38 +4395,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130344254</v>
+        <v>130344259</v>
       </c>
       <c r="B37" t="n">
-        <v>57823</v>
+        <v>98920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4444,10 +4439,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633695</v>
+        <v>633692</v>
       </c>
       <c r="R37" t="n">
-        <v>6658733</v>
+        <v>6658641</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,7 +4474,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4489,7 +4484,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -3683,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B31" t="n">
         <v>98920</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R31" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,7 +3772,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3787,19 +3792,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B32" t="n">
         <v>98920</v>
@@ -3829,7 +3834,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3843,10 +3848,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R32" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3888,12 +3893,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>130140331</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>130140320</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130140318</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>130140309</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>130140296</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>130140327</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>130344257</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>130140325</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>130140340</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,32 +1937,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140343</v>
+        <v>130140292</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>97169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633719</v>
+        <v>633626</v>
       </c>
       <c r="R14" t="n">
-        <v>6658699</v>
+        <v>6658697</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2008,11 +2008,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,32 +2034,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130140315</v>
+        <v>130140343</v>
       </c>
       <c r="B15" t="n">
-        <v>97791</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633550</v>
+        <v>633719</v>
       </c>
       <c r="R15" t="n">
-        <v>6658729</v>
+        <v>6658699</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2110,6 +2105,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2136,32 +2136,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130140292</v>
+        <v>130140315</v>
       </c>
       <c r="B16" t="n">
-        <v>97166</v>
+        <v>97794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633626</v>
+        <v>633550</v>
       </c>
       <c r="R16" t="n">
-        <v>6658697</v>
+        <v>6658729</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2233,32 +2233,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140344</v>
+        <v>130140312</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>97794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633720</v>
+        <v>633608</v>
       </c>
       <c r="R17" t="n">
-        <v>6658686</v>
+        <v>6658722</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2304,11 +2304,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140339</v>
+        <v>130140344</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2370,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633700</v>
+        <v>633720</v>
       </c>
       <c r="R18" t="n">
-        <v>6658589</v>
+        <v>6658686</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2410,7 +2405,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10 buketter 1310</t>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,32 +2432,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130140312</v>
+        <v>130140339</v>
       </c>
       <c r="B19" t="n">
-        <v>97791</v>
+        <v>98923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2472,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633608</v>
+        <v>633700</v>
       </c>
       <c r="R19" t="n">
-        <v>6658722</v>
+        <v>6658589</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2508,6 +2503,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10 buketter 1310</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130140322</v>
+        <v>130140336</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633712</v>
+        <v>633697</v>
       </c>
       <c r="R20" t="n">
-        <v>6658740</v>
+        <v>6658591</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>7 buketter 1242</t>
+          <t>15 buketter 1309</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130140336</v>
+        <v>130140322</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633697</v>
+        <v>633712</v>
       </c>
       <c r="R21" t="n">
-        <v>6658591</v>
+        <v>6658740</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>15 buketter 1309</t>
+          <t>7 buketter 1242</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,7 +2935,7 @@
         <v>130294382</v>
       </c>
       <c r="B24" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130352567</v>
       </c>
       <c r="B28" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>130344256</v>
       </c>
       <c r="B29" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>130352566</v>
       </c>
       <c r="B30" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>130344255</v>
       </c>
       <c r="B31" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>130352569</v>
       </c>
       <c r="B32" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>130344261</v>
       </c>
       <c r="B33" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130344252</v>
       </c>
       <c r="B34" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130344262</v>
       </c>
       <c r="B35" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>130344259</v>
       </c>
       <c r="B37" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>130352568</v>
       </c>
       <c r="B38" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>130352572</v>
       </c>
       <c r="B39" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>130344251</v>
       </c>
       <c r="B40" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>130140331</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>130140320</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130140318</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>130140309</v>
       </c>
       <c r="B7" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>130140296</v>
       </c>
       <c r="B8" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>130140327</v>
       </c>
       <c r="B9" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>130344257</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>130140325</v>
       </c>
       <c r="B11" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>130140298</v>
       </c>
       <c r="B12" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>130140340</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,32 +1937,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140292</v>
+        <v>130140343</v>
       </c>
       <c r="B14" t="n">
-        <v>97169</v>
+        <v>98949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633626</v>
+        <v>633719</v>
       </c>
       <c r="R14" t="n">
-        <v>6658697</v>
+        <v>6658699</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2008,6 +2008,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2034,32 +2039,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130140343</v>
+        <v>130140315</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>97820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633719</v>
+        <v>633550</v>
       </c>
       <c r="R15" t="n">
-        <v>6658699</v>
+        <v>6658729</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2105,11 +2110,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2136,32 +2136,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130140315</v>
+        <v>130140292</v>
       </c>
       <c r="B16" t="n">
-        <v>97794</v>
+        <v>97195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633550</v>
+        <v>633626</v>
       </c>
       <c r="R16" t="n">
-        <v>6658729</v>
+        <v>6658697</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2233,32 +2233,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140312</v>
+        <v>130140344</v>
       </c>
       <c r="B17" t="n">
-        <v>97794</v>
+        <v>98949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633608</v>
+        <v>633720</v>
       </c>
       <c r="R17" t="n">
-        <v>6658722</v>
+        <v>6658686</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2304,6 +2304,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,10 +2335,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140344</v>
+        <v>130140339</v>
       </c>
       <c r="B18" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633720</v>
+        <v>633700</v>
       </c>
       <c r="R18" t="n">
-        <v>6658686</v>
+        <v>6658589</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2405,7 +2410,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bukett 1301</t>
+          <t>10 buketter 1310</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,32 +2437,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130140339</v>
+        <v>130140312</v>
       </c>
       <c r="B19" t="n">
-        <v>98923</v>
+        <v>97820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633700</v>
+        <v>633608</v>
       </c>
       <c r="R19" t="n">
-        <v>6658589</v>
+        <v>6658722</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2503,11 +2508,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10 buketter 1310</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130140336</v>
+        <v>130140322</v>
       </c>
       <c r="B20" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633697</v>
+        <v>633712</v>
       </c>
       <c r="R20" t="n">
-        <v>6658591</v>
+        <v>6658740</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>15 buketter 1309</t>
+          <t>7 buketter 1242</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130140322</v>
+        <v>130140336</v>
       </c>
       <c r="B21" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633712</v>
+        <v>633697</v>
       </c>
       <c r="R21" t="n">
-        <v>6658740</v>
+        <v>6658591</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>7 buketter 1242</t>
+          <t>15 buketter 1309</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2741,7 +2741,7 @@
         <v>130140303</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>130140307</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>130294382</v>
       </c>
       <c r="B24" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>130294380</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>130294381</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130352567</v>
       </c>
       <c r="B28" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>130344256</v>
       </c>
       <c r="B29" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>130352566</v>
       </c>
       <c r="B30" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>130344255</v>
       </c>
       <c r="B31" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>130352569</v>
       </c>
       <c r="B32" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,10 +3920,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130344261</v>
+        <v>130344252</v>
       </c>
       <c r="B33" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>633704</v>
+        <v>633696</v>
       </c>
       <c r="R33" t="n">
-        <v>6658632</v>
+        <v>6658741</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4041,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130344252</v>
+        <v>130344261</v>
       </c>
       <c r="B34" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>633696</v>
+        <v>633704</v>
       </c>
       <c r="R34" t="n">
-        <v>6658741</v>
+        <v>6658632</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4165,7 +4165,7 @@
         <v>130344262</v>
       </c>
       <c r="B35" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>130344254</v>
       </c>
       <c r="B36" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>130344259</v>
       </c>
       <c r="B37" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130352568</v>
+        <v>130344251</v>
       </c>
       <c r="B38" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633653</v>
+        <v>633706</v>
       </c>
       <c r="R38" t="n">
-        <v>6658661</v>
+        <v>6658752</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4620,22 +4625,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352572</v>
+        <v>130352568</v>
       </c>
       <c r="B39" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4662,7 +4667,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4672,14 +4677,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633680</v>
+        <v>633653</v>
       </c>
       <c r="R39" t="n">
-        <v>6658562</v>
+        <v>6658661</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,7 +4716,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4721,7 +4726,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4748,10 +4753,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130344251</v>
+        <v>130352572</v>
       </c>
       <c r="B40" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4778,7 +4783,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4788,14 +4793,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633706</v>
+        <v>633680</v>
       </c>
       <c r="R40" t="n">
-        <v>6658752</v>
+        <v>6658562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4827,7 +4832,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4837,12 +4842,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
         <v>130344249</v>
       </c>
       <c r="B41" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>130344260</v>
       </c>
       <c r="B42" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -1937,32 +1937,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140343</v>
+        <v>130140292</v>
       </c>
       <c r="B14" t="n">
-        <v>98949</v>
+        <v>97195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633719</v>
+        <v>633626</v>
       </c>
       <c r="R14" t="n">
-        <v>6658699</v>
+        <v>6658697</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2008,11 +2008,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,32 +2131,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130140292</v>
+        <v>130140343</v>
       </c>
       <c r="B16" t="n">
-        <v>97195</v>
+        <v>98949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633626</v>
+        <v>633719</v>
       </c>
       <c r="R16" t="n">
-        <v>6658697</v>
+        <v>6658699</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2207,6 +2202,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>130140331</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>130140320</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130140318</v>
       </c>
       <c r="B6" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>130140309</v>
       </c>
       <c r="B7" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>130140296</v>
       </c>
       <c r="B8" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>130140327</v>
       </c>
       <c r="B9" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>130344257</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>130140325</v>
       </c>
       <c r="B11" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>130140340</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,32 +1937,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140292</v>
+        <v>130140343</v>
       </c>
       <c r="B14" t="n">
-        <v>97195</v>
+        <v>98950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633626</v>
+        <v>633719</v>
       </c>
       <c r="R14" t="n">
-        <v>6658697</v>
+        <v>6658699</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2008,6 +2008,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2037,7 +2042,7 @@
         <v>130140315</v>
       </c>
       <c r="B15" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,32 +2136,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130140343</v>
+        <v>130140292</v>
       </c>
       <c r="B16" t="n">
-        <v>98949</v>
+        <v>97196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633719</v>
+        <v>633626</v>
       </c>
       <c r="R16" t="n">
-        <v>6658699</v>
+        <v>6658697</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2202,11 +2207,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2236,7 +2236,7 @@
         <v>130140344</v>
       </c>
       <c r="B17" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>130140339</v>
       </c>
       <c r="B18" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>130140312</v>
       </c>
       <c r="B19" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130140322</v>
+        <v>130140336</v>
       </c>
       <c r="B20" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633712</v>
+        <v>633697</v>
       </c>
       <c r="R20" t="n">
-        <v>6658740</v>
+        <v>6658591</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>7 buketter 1242</t>
+          <t>15 buketter 1309</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130140336</v>
+        <v>130140322</v>
       </c>
       <c r="B21" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633697</v>
+        <v>633712</v>
       </c>
       <c r="R21" t="n">
-        <v>6658591</v>
+        <v>6658740</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>15 buketter 1309</t>
+          <t>7 buketter 1242</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,7 +2935,7 @@
         <v>130294382</v>
       </c>
       <c r="B24" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130352567</v>
       </c>
       <c r="B28" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>130344256</v>
       </c>
       <c r="B29" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>130352566</v>
       </c>
       <c r="B30" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B31" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R31" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,12 +3772,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3792,22 +3787,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B32" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3848,10 +3843,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R32" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3893,7 +3888,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3923,7 +3923,7 @@
         <v>130344252</v>
       </c>
       <c r="B33" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130344261</v>
       </c>
       <c r="B34" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130344262</v>
       </c>
       <c r="B35" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>130344259</v>
       </c>
       <c r="B37" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130344251</v>
+        <v>130352568</v>
       </c>
       <c r="B38" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633706</v>
+        <v>633653</v>
       </c>
       <c r="R38" t="n">
-        <v>6658752</v>
+        <v>6658661</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,12 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4625,22 +4620,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352568</v>
+        <v>130352572</v>
       </c>
       <c r="B39" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4667,7 +4662,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4677,14 +4672,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633653</v>
+        <v>633680</v>
       </c>
       <c r="R39" t="n">
-        <v>6658661</v>
+        <v>6658562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,7 +4711,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4726,7 +4721,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,10 +4748,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130352572</v>
+        <v>130344251</v>
       </c>
       <c r="B40" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4783,7 +4778,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4793,14 +4788,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633680</v>
+        <v>633706</v>
       </c>
       <c r="R40" t="n">
-        <v>6658562</v>
+        <v>6658752</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4832,7 +4827,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4842,7 +4837,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -1518,7 +1518,7 @@
         <v>130344257</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>130294382</v>
       </c>
       <c r="B24" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130352567</v>
       </c>
       <c r="B28" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>130344256</v>
       </c>
       <c r="B29" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>130352566</v>
       </c>
       <c r="B30" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>130352569</v>
       </c>
       <c r="B31" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>130344255</v>
       </c>
       <c r="B32" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>130344252</v>
       </c>
       <c r="B33" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130344261</v>
       </c>
       <c r="B34" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130344262</v>
       </c>
       <c r="B35" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,38 +4283,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130344254</v>
+        <v>130344259</v>
       </c>
       <c r="B36" t="n">
-        <v>57849</v>
+        <v>98951</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4323,10 +4327,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633695</v>
+        <v>633692</v>
       </c>
       <c r="R36" t="n">
-        <v>6658733</v>
+        <v>6658641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,7 +4362,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4368,7 +4372,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,42 +4404,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130344259</v>
+        <v>130344254</v>
       </c>
       <c r="B37" t="n">
-        <v>98950</v>
+        <v>57849</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4439,10 +4444,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633692</v>
+        <v>633695</v>
       </c>
       <c r="R37" t="n">
-        <v>6658641</v>
+        <v>6658733</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4479,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4484,12 +4489,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4519,7 +4519,7 @@
         <v>130352568</v>
       </c>
       <c r="B38" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>130352572</v>
       </c>
       <c r="B39" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>130344251</v>
       </c>
       <c r="B40" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -1518,7 +1518,7 @@
         <v>130344257</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>130294382</v>
       </c>
       <c r="B24" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>130294380</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>130294381</v>
       </c>
       <c r="B26" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130352567</v>
       </c>
       <c r="B28" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>130344256</v>
       </c>
       <c r="B29" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>130352566</v>
       </c>
       <c r="B30" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B31" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R31" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,7 +3772,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3787,22 +3792,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B32" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3843,10 +3848,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R32" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3888,12 +3893,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3923,7 +3923,7 @@
         <v>130344252</v>
       </c>
       <c r="B33" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130344261</v>
       </c>
       <c r="B34" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130344262</v>
       </c>
       <c r="B35" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,42 +4283,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130344259</v>
+        <v>130344254</v>
       </c>
       <c r="B36" t="n">
-        <v>98951</v>
+        <v>57851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4327,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633692</v>
+        <v>633695</v>
       </c>
       <c r="R36" t="n">
-        <v>6658641</v>
+        <v>6658733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4362,7 +4358,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4372,12 +4368,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4404,38 +4395,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130344254</v>
+        <v>130344259</v>
       </c>
       <c r="B37" t="n">
-        <v>57849</v>
+        <v>98953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4444,10 +4439,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633695</v>
+        <v>633692</v>
       </c>
       <c r="R37" t="n">
-        <v>6658733</v>
+        <v>6658641</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,7 +4474,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4489,7 +4484,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130352568</v>
+        <v>130344251</v>
       </c>
       <c r="B38" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633653</v>
+        <v>633706</v>
       </c>
       <c r="R38" t="n">
-        <v>6658661</v>
+        <v>6658752</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4620,22 +4625,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352572</v>
+        <v>130352568</v>
       </c>
       <c r="B39" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4662,7 +4667,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4672,14 +4677,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633680</v>
+        <v>633653</v>
       </c>
       <c r="R39" t="n">
-        <v>6658562</v>
+        <v>6658661</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,7 +4716,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4721,7 +4726,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4748,10 +4753,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130344251</v>
+        <v>130352572</v>
       </c>
       <c r="B40" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4778,7 +4783,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4788,14 +4793,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633706</v>
+        <v>633680</v>
       </c>
       <c r="R40" t="n">
-        <v>6658752</v>
+        <v>6658562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4827,7 +4832,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4837,12 +4842,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
         <v>130344249</v>
       </c>
       <c r="B41" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>130344260</v>
       </c>
       <c r="B42" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -1518,7 +1518,7 @@
         <v>130344257</v>
       </c>
       <c r="B10" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>130294382</v>
       </c>
       <c r="B24" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130352567</v>
       </c>
       <c r="B28" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>130344256</v>
       </c>
       <c r="B29" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>130352566</v>
       </c>
       <c r="B30" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>130344255</v>
       </c>
       <c r="B31" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>130352569</v>
       </c>
       <c r="B32" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>130344252</v>
       </c>
       <c r="B33" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130344261</v>
       </c>
       <c r="B34" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130344262</v>
       </c>
       <c r="B35" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>130344259</v>
       </c>
       <c r="B37" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>130344251</v>
       </c>
       <c r="B38" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>130352568</v>
       </c>
       <c r="B39" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>130352572</v>
       </c>
       <c r="B40" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -3683,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B31" t="n">
         <v>98957</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R31" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,12 +3772,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3792,19 +3787,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B32" t="n">
         <v>98957</v>
@@ -3834,7 +3829,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3848,10 +3843,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R32" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3893,7 +3888,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4283,38 +4283,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130344254</v>
+        <v>130344259</v>
       </c>
       <c r="B36" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4323,10 +4327,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633695</v>
+        <v>633692</v>
       </c>
       <c r="R36" t="n">
-        <v>6658733</v>
+        <v>6658641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,7 +4362,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4368,7 +4372,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,42 +4404,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130344259</v>
+        <v>130344254</v>
       </c>
       <c r="B37" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4439,10 +4444,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633692</v>
+        <v>633695</v>
       </c>
       <c r="R37" t="n">
-        <v>6658641</v>
+        <v>6658733</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4479,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4484,12 +4489,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -4283,42 +4283,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130344259</v>
+        <v>130344254</v>
       </c>
       <c r="B36" t="n">
-        <v>98957</v>
+        <v>57851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4327,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633692</v>
+        <v>633695</v>
       </c>
       <c r="R36" t="n">
-        <v>6658641</v>
+        <v>6658733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4362,7 +4358,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4372,12 +4368,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4404,38 +4395,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130344254</v>
+        <v>130344259</v>
       </c>
       <c r="B37" t="n">
-        <v>57851</v>
+        <v>98957</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4444,10 +4439,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633695</v>
+        <v>633692</v>
       </c>
       <c r="R37" t="n">
-        <v>6658733</v>
+        <v>6658641</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,7 +4474,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4489,7 +4484,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,7 +4516,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130344251</v>
+        <v>130352568</v>
       </c>
       <c r="B38" t="n">
         <v>98957</v>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633706</v>
+        <v>633653</v>
       </c>
       <c r="R38" t="n">
-        <v>6658752</v>
+        <v>6658661</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,12 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4625,19 +4620,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352568</v>
+        <v>130352572</v>
       </c>
       <c r="B39" t="n">
         <v>98957</v>
@@ -4667,7 +4662,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4677,14 +4672,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633653</v>
+        <v>633680</v>
       </c>
       <c r="R39" t="n">
-        <v>6658661</v>
+        <v>6658562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,7 +4711,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4726,7 +4721,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,7 +4748,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130352572</v>
+        <v>130344251</v>
       </c>
       <c r="B40" t="n">
         <v>98957</v>
@@ -4783,7 +4778,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4793,14 +4788,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633680</v>
+        <v>633706</v>
       </c>
       <c r="R40" t="n">
-        <v>6658562</v>
+        <v>6658752</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4832,7 +4827,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4842,7 +4837,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -3683,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B31" t="n">
         <v>98957</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R31" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,7 +3772,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3787,19 +3792,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B32" t="n">
         <v>98957</v>
@@ -3829,7 +3834,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3843,10 +3848,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R32" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3888,12 +3893,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130352568</v>
+        <v>130344251</v>
       </c>
       <c r="B38" t="n">
         <v>98957</v>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633653</v>
+        <v>633706</v>
       </c>
       <c r="R38" t="n">
-        <v>6658661</v>
+        <v>6658752</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4620,19 +4625,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352572</v>
+        <v>130352568</v>
       </c>
       <c r="B39" t="n">
         <v>98957</v>
@@ -4662,7 +4667,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4672,14 +4677,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633680</v>
+        <v>633653</v>
       </c>
       <c r="R39" t="n">
-        <v>6658562</v>
+        <v>6658661</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,7 +4716,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4721,7 +4726,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4748,7 +4753,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130344251</v>
+        <v>130352572</v>
       </c>
       <c r="B40" t="n">
         <v>98957</v>
@@ -4778,7 +4783,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4788,14 +4793,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633706</v>
+        <v>633680</v>
       </c>
       <c r="R40" t="n">
-        <v>6658752</v>
+        <v>6658562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4827,7 +4832,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4837,12 +4842,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -1518,7 +1518,7 @@
         <v>130344257</v>
       </c>
       <c r="B10" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>130294382</v>
       </c>
       <c r="B24" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>130294380</v>
       </c>
       <c r="B25" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>130294381</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130352567</v>
       </c>
       <c r="B28" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>130344256</v>
       </c>
       <c r="B29" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>130352566</v>
       </c>
       <c r="B30" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B31" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R31" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,12 +3772,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3792,22 +3787,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B32" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3848,10 +3843,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R32" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3893,7 +3888,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3923,7 +3923,7 @@
         <v>130344252</v>
       </c>
       <c r="B33" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130344261</v>
       </c>
       <c r="B34" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130344262</v>
       </c>
       <c r="B35" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,38 +4283,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130344254</v>
+        <v>130344259</v>
       </c>
       <c r="B36" t="n">
-        <v>57851</v>
+        <v>98970</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4323,10 +4327,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633695</v>
+        <v>633692</v>
       </c>
       <c r="R36" t="n">
-        <v>6658733</v>
+        <v>6658641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,7 +4362,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4368,7 +4372,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,42 +4404,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130344259</v>
+        <v>130344254</v>
       </c>
       <c r="B37" t="n">
-        <v>98957</v>
+        <v>57859</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4439,10 +4444,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633692</v>
+        <v>633695</v>
       </c>
       <c r="R37" t="n">
-        <v>6658641</v>
+        <v>6658733</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4479,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4484,12 +4489,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130344251</v>
+        <v>130352568</v>
       </c>
       <c r="B38" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633706</v>
+        <v>633653</v>
       </c>
       <c r="R38" t="n">
-        <v>6658752</v>
+        <v>6658661</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,12 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4625,22 +4620,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352568</v>
+        <v>130352572</v>
       </c>
       <c r="B39" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4667,7 +4662,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4677,14 +4672,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633653</v>
+        <v>633680</v>
       </c>
       <c r="R39" t="n">
-        <v>6658661</v>
+        <v>6658562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,7 +4711,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4726,7 +4721,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,10 +4748,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130352572</v>
+        <v>130344251</v>
       </c>
       <c r="B40" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4783,7 +4778,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4793,14 +4788,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633680</v>
+        <v>633706</v>
       </c>
       <c r="R40" t="n">
-        <v>6658562</v>
+        <v>6658752</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4832,7 +4827,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4842,7 +4837,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
         <v>130344249</v>
       </c>
       <c r="B41" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>130344260</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -1518,7 +1518,7 @@
         <v>130344257</v>
       </c>
       <c r="B10" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>130294382</v>
       </c>
       <c r="B24" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>130294380</v>
       </c>
       <c r="B25" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>130294381</v>
       </c>
       <c r="B26" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130352567</v>
       </c>
       <c r="B28" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>130344256</v>
       </c>
       <c r="B29" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>130352566</v>
       </c>
       <c r="B30" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B31" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R31" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,7 +3772,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3787,22 +3792,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B32" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3843,10 +3848,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R32" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3888,12 +3893,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3923,7 +3923,7 @@
         <v>130344252</v>
       </c>
       <c r="B33" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130344261</v>
       </c>
       <c r="B34" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130344262</v>
       </c>
       <c r="B35" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4283,42 +4283,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130344259</v>
+        <v>130344254</v>
       </c>
       <c r="B36" t="n">
-        <v>98970</v>
+        <v>57860</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4327,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633692</v>
+        <v>633695</v>
       </c>
       <c r="R36" t="n">
-        <v>6658641</v>
+        <v>6658733</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4362,7 +4358,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4372,12 +4368,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4404,38 +4395,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130344254</v>
+        <v>130344259</v>
       </c>
       <c r="B37" t="n">
-        <v>57859</v>
+        <v>98971</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4444,10 +4439,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633695</v>
+        <v>633692</v>
       </c>
       <c r="R37" t="n">
-        <v>6658733</v>
+        <v>6658641</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4479,7 +4474,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4489,7 +4484,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4516,10 +4516,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130352568</v>
+        <v>130344251</v>
       </c>
       <c r="B38" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633653</v>
+        <v>633706</v>
       </c>
       <c r="R38" t="n">
-        <v>6658661</v>
+        <v>6658752</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4620,22 +4625,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352572</v>
+        <v>130352568</v>
       </c>
       <c r="B39" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4662,7 +4667,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4672,14 +4677,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633680</v>
+        <v>633653</v>
       </c>
       <c r="R39" t="n">
-        <v>6658562</v>
+        <v>6658661</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,7 +4716,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4721,7 +4726,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4748,10 +4753,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130344251</v>
+        <v>130352572</v>
       </c>
       <c r="B40" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4778,7 +4783,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4788,14 +4793,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633706</v>
+        <v>633680</v>
       </c>
       <c r="R40" t="n">
-        <v>6658752</v>
+        <v>6658562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4827,7 +4832,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4837,12 +4842,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4872,7 +4872,7 @@
         <v>130344249</v>
       </c>
       <c r="B41" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>130344260</v>
       </c>
       <c r="B42" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -1518,7 +1518,7 @@
         <v>130344257</v>
       </c>
       <c r="B10" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>130294382</v>
       </c>
       <c r="B24" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>130294380</v>
       </c>
       <c r="B25" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>130294381</v>
       </c>
       <c r="B26" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>130352567</v>
       </c>
       <c r="B28" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>130344256</v>
       </c>
       <c r="B29" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>130352566</v>
       </c>
       <c r="B30" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>130344255</v>
       </c>
       <c r="B31" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>130352569</v>
       </c>
       <c r="B32" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>130344252</v>
       </c>
       <c r="B33" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130344261</v>
       </c>
       <c r="B34" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130344262</v>
       </c>
       <c r="B35" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>130344254</v>
       </c>
       <c r="B36" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>130344259</v>
       </c>
       <c r="B37" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>130344251</v>
       </c>
       <c r="B38" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>130352568</v>
       </c>
       <c r="B39" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>130352572</v>
       </c>
       <c r="B40" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>130344249</v>
       </c>
       <c r="B41" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>130344260</v>
       </c>
       <c r="B42" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -3683,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B31" t="n">
         <v>98974</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R31" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,12 +3772,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3792,19 +3787,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B32" t="n">
         <v>98974</v>
@@ -3834,7 +3829,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3848,10 +3843,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R32" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3883,7 +3878,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3893,7 +3888,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -4516,7 +4516,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130344251</v>
+        <v>130352568</v>
       </c>
       <c r="B38" t="n">
         <v>98974</v>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633706</v>
+        <v>633653</v>
       </c>
       <c r="R38" t="n">
-        <v>6658752</v>
+        <v>6658661</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,12 +4605,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4625,19 +4620,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352568</v>
+        <v>130352572</v>
       </c>
       <c r="B39" t="n">
         <v>98974</v>
@@ -4667,7 +4662,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4677,14 +4672,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633653</v>
+        <v>633680</v>
       </c>
       <c r="R39" t="n">
-        <v>6658661</v>
+        <v>6658562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,7 +4711,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4726,7 +4721,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,7 +4748,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130352572</v>
+        <v>130344251</v>
       </c>
       <c r="B40" t="n">
         <v>98974</v>
@@ -4783,7 +4778,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4793,14 +4788,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633680</v>
+        <v>633706</v>
       </c>
       <c r="R40" t="n">
-        <v>6658562</v>
+        <v>6658752</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4832,7 +4827,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4842,7 +4837,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -3683,7 +3683,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B31" t="n">
         <v>98974</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R31" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,7 +3772,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3787,19 +3792,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130344255</v>
+        <v>130352569</v>
       </c>
       <c r="B32" t="n">
         <v>98974</v>
@@ -3829,7 +3834,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3843,10 +3848,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633703</v>
+        <v>633693</v>
       </c>
       <c r="R32" t="n">
-        <v>6658736</v>
+        <v>6658643</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,7 +3883,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3888,12 +3893,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130352568</v>
+        <v>130344251</v>
       </c>
       <c r="B38" t="n">
         <v>98974</v>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633653</v>
+        <v>633706</v>
       </c>
       <c r="R38" t="n">
-        <v>6658661</v>
+        <v>6658752</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,7 +4605,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4620,19 +4625,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352572</v>
+        <v>130352568</v>
       </c>
       <c r="B39" t="n">
         <v>98974</v>
@@ -4662,7 +4667,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4672,14 +4677,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633680</v>
+        <v>633653</v>
       </c>
       <c r="R39" t="n">
-        <v>6658562</v>
+        <v>6658661</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,7 +4716,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4721,7 +4726,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4748,7 +4753,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130344251</v>
+        <v>130352572</v>
       </c>
       <c r="B40" t="n">
         <v>98974</v>
@@ -4778,7 +4783,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4788,14 +4793,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633706</v>
+        <v>633680</v>
       </c>
       <c r="R40" t="n">
-        <v>6658752</v>
+        <v>6658562</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4827,7 +4832,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4837,12 +4842,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,12 +4857,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -5096,7 +5096,7 @@
         <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>98974</v>
+        <v>98988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>130354986</v>
       </c>
       <c r="B44" t="n">
-        <v>97220</v>
+        <v>97229</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,34 +1117,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130140318</v>
+        <v>130140317</v>
       </c>
       <c r="B6" t="n">
-        <v>98950</v>
+        <v>97815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221944</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633681</v>
+        <v>633634</v>
       </c>
       <c r="R6" t="n">
-        <v>6658735</v>
+        <v>6658696</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1188,11 +1184,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>9 buketter 1252</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130140309</v>
+        <v>130140318</v>
       </c>
       <c r="B7" t="n">
-        <v>92211</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633716</v>
+        <v>633681</v>
       </c>
       <c r="R7" t="n">
-        <v>6658639</v>
+        <v>6658735</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>9 buketter 1252</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,32 +1312,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130140296</v>
+        <v>130140309</v>
       </c>
       <c r="B8" t="n">
-        <v>91758</v>
+        <v>92211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130140327</v>
+        <v>130140296</v>
       </c>
       <c r="B9" t="n">
-        <v>98950</v>
+        <v>91758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633701</v>
+        <v>633716</v>
       </c>
       <c r="R9" t="n">
-        <v>6658658</v>
+        <v>6658639</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1484,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>4 buketter 1318</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130344257</v>
+        <v>130140327</v>
       </c>
       <c r="B10" t="n">
-        <v>98974</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1543,29 +1534,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633672</v>
+        <v>633701</v>
       </c>
       <c r="R10" t="n">
-        <v>6658700</v>
+        <v>6658658</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,27 +1571,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>skott</t>
+          <t>4 buketter 1318</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,22 +1596,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130140325</v>
+        <v>130344257</v>
       </c>
       <c r="B11" t="n">
-        <v>98950</v>
+        <v>98974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,20 +1636,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633718</v>
+        <v>633672</v>
       </c>
       <c r="R11" t="n">
-        <v>6658738</v>
+        <v>6658700</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1701,17 +1682,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>5 buketter 1244</t>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,44 +1717,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130140298</v>
+        <v>130140325</v>
       </c>
       <c r="B12" t="n">
-        <v>58011</v>
+        <v>98950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633710</v>
+        <v>633718</v>
       </c>
       <c r="R12" t="n">
-        <v>6658772</v>
+        <v>6658738</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1809,6 +1800,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5 buketter 1244</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,32 +1831,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130140340</v>
+        <v>130140298</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>58011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1870,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633707</v>
+        <v>633710</v>
       </c>
       <c r="R13" t="n">
-        <v>6658726</v>
+        <v>6658772</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1906,11 +1902,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>10 buketter 1247</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,7 +1928,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140343</v>
+        <v>130140340</v>
       </c>
       <c r="B14" t="n">
         <v>98950</v>
@@ -1972,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633719</v>
+        <v>633707</v>
       </c>
       <c r="R14" t="n">
-        <v>6658699</v>
+        <v>6658726</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2012,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1 bukett 1301</t>
+          <t>10 buketter 1247</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,32 +2030,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130140315</v>
+        <v>130140343</v>
       </c>
       <c r="B15" t="n">
-        <v>97821</v>
+        <v>98950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633550</v>
+        <v>633719</v>
       </c>
       <c r="R15" t="n">
-        <v>6658729</v>
+        <v>6658699</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2110,6 +2101,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2136,32 +2132,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130140292</v>
+        <v>130140315</v>
       </c>
       <c r="B16" t="n">
-        <v>97196</v>
+        <v>97821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633626</v>
+        <v>633550</v>
       </c>
       <c r="R16" t="n">
-        <v>6658697</v>
+        <v>6658729</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2233,32 +2229,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140344</v>
+        <v>130140292</v>
       </c>
       <c r="B17" t="n">
-        <v>98950</v>
+        <v>97196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633720</v>
+        <v>633626</v>
       </c>
       <c r="R17" t="n">
-        <v>6658686</v>
+        <v>6658697</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2304,11 +2300,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,7 +2326,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140339</v>
+        <v>130140344</v>
       </c>
       <c r="B18" t="n">
         <v>98950</v>
@@ -2370,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633700</v>
+        <v>633720</v>
       </c>
       <c r="R18" t="n">
-        <v>6658589</v>
+        <v>6658686</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2410,7 +2401,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10 buketter 1310</t>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,32 +2428,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130140312</v>
+        <v>130140339</v>
       </c>
       <c r="B19" t="n">
-        <v>97821</v>
+        <v>98950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2472,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633608</v>
+        <v>633700</v>
       </c>
       <c r="R19" t="n">
-        <v>6658722</v>
+        <v>6658589</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2508,6 +2499,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10 buketter 1310</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,32 +2530,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130140336</v>
+        <v>130140312</v>
       </c>
       <c r="B20" t="n">
-        <v>98950</v>
+        <v>97821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633697</v>
+        <v>633608</v>
       </c>
       <c r="R20" t="n">
-        <v>6658591</v>
+        <v>6658722</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2605,11 +2601,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>15 buketter 1309</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,7 +2627,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130140322</v>
+        <v>130140336</v>
       </c>
       <c r="B21" t="n">
         <v>98950</v>
@@ -2671,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633712</v>
+        <v>633697</v>
       </c>
       <c r="R21" t="n">
-        <v>6658740</v>
+        <v>6658591</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2711,7 +2702,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>7 buketter 1242</t>
+          <t>15 buketter 1309</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,32 +2729,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130140303</v>
+        <v>130140322</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>98950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633595</v>
+        <v>633712</v>
       </c>
       <c r="R22" t="n">
-        <v>6658626</v>
+        <v>6658740</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2809,6 +2800,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>7 buketter 1242</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,34 +2831,30 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130140307</v>
+        <v>130140316</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>97815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2870,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633545</v>
+        <v>633655</v>
       </c>
       <c r="R23" t="n">
-        <v>6658735</v>
+        <v>6658641</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2895,7 +2887,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2932,32 +2924,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130294382</v>
+        <v>130140303</v>
       </c>
       <c r="B24" t="n">
-        <v>98974</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2967,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633614</v>
+        <v>633595</v>
       </c>
       <c r="R24" t="n">
-        <v>6658718</v>
+        <v>6658626</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2997,17 +2989,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>6 buketter</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3034,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130294380</v>
+        <v>130140307</v>
       </c>
       <c r="B25" t="n">
-        <v>57861</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3069,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633664</v>
+        <v>633545</v>
       </c>
       <c r="R25" t="n">
-        <v>6658700</v>
+        <v>6658735</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3094,17 +3081,17 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3131,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130294381</v>
+        <v>130294382</v>
       </c>
       <c r="B26" t="n">
-        <v>57861</v>
+        <v>98974</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3166,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633661</v>
+        <v>633614</v>
       </c>
       <c r="R26" t="n">
-        <v>6658817</v>
+        <v>6658718</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3202,6 +3189,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3228,32 +3220,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130294384</v>
+        <v>130294380</v>
       </c>
       <c r="B27" t="n">
-        <v>4779</v>
+        <v>57861</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3263,10 +3255,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633647</v>
+        <v>633664</v>
       </c>
       <c r="R27" t="n">
-        <v>6658734</v>
+        <v>6658700</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3299,11 +3291,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3330,57 +3317,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130352567</v>
+        <v>130294381</v>
       </c>
       <c r="B28" t="n">
-        <v>98974</v>
+        <v>57861</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>633640</v>
+        <v>633661</v>
       </c>
       <c r="R28" t="n">
-        <v>6658662</v>
+        <v>6658817</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3404,22 +3382,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3434,69 +3402,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130344256</v>
+        <v>130294384</v>
       </c>
       <c r="B29" t="n">
-        <v>98974</v>
+        <v>4779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>633669</v>
+        <v>633647</v>
       </c>
       <c r="R29" t="n">
-        <v>6658717</v>
+        <v>6658734</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3520,27 +3479,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>skott</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,19 +3504,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130352566</v>
+        <v>130352567</v>
       </c>
       <c r="B30" t="n">
         <v>98974</v>
@@ -3597,7 +3546,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3611,10 +3560,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>633645</v>
+        <v>633640</v>
       </c>
       <c r="R30" t="n">
-        <v>6658739</v>
+        <v>6658662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3646,7 +3595,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3656,7 +3605,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,7 +3632,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130352569</v>
+        <v>130344256</v>
       </c>
       <c r="B31" t="n">
         <v>98974</v>
@@ -3713,7 +3662,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3727,10 +3676,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633693</v>
+        <v>633669</v>
       </c>
       <c r="R31" t="n">
-        <v>6658643</v>
+        <v>6658717</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,7 +3711,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3772,7 +3721,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3787,19 +3741,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130344255</v>
+        <v>130352566</v>
       </c>
       <c r="B32" t="n">
         <v>98974</v>
@@ -3829,7 +3783,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3843,10 +3797,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633703</v>
+        <v>633645</v>
       </c>
       <c r="R32" t="n">
-        <v>6658736</v>
+        <v>6658739</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,7 +3832,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3888,12 +3842,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,19 +3857,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130344252</v>
+        <v>130352569</v>
       </c>
       <c r="B33" t="n">
         <v>98974</v>
@@ -3950,7 +3899,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3964,10 +3913,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>633696</v>
+        <v>633693</v>
       </c>
       <c r="R33" t="n">
-        <v>6658741</v>
+        <v>6658643</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3999,7 +3948,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4009,12 +3958,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4029,19 +3973,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130344261</v>
+        <v>130344255</v>
       </c>
       <c r="B34" t="n">
         <v>98974</v>
@@ -4085,10 +4029,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>633704</v>
+        <v>633703</v>
       </c>
       <c r="R34" t="n">
-        <v>6658632</v>
+        <v>6658736</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4120,7 +4064,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4130,7 +4074,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4162,7 +4106,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130344262</v>
+        <v>130344252</v>
       </c>
       <c r="B35" t="n">
         <v>98974</v>
@@ -4192,7 +4136,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4206,10 +4150,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>633708</v>
+        <v>633696</v>
       </c>
       <c r="R35" t="n">
-        <v>6658599</v>
+        <v>6658741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4241,7 +4185,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4251,7 +4195,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4283,38 +4227,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130344254</v>
+        <v>130344261</v>
       </c>
       <c r="B36" t="n">
-        <v>57861</v>
+        <v>98974</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4323,10 +4271,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>633695</v>
+        <v>633704</v>
       </c>
       <c r="R36" t="n">
-        <v>6658733</v>
+        <v>6658632</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,7 +4306,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4368,7 +4316,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,7 +4348,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130344259</v>
+        <v>130344262</v>
       </c>
       <c r="B37" t="n">
         <v>98974</v>
@@ -4425,7 +4378,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4439,10 +4392,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>633692</v>
+        <v>633708</v>
       </c>
       <c r="R37" t="n">
-        <v>6658641</v>
+        <v>6658599</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4427,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4484,7 +4437,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4516,42 +4469,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130344251</v>
+        <v>130344254</v>
       </c>
       <c r="B38" t="n">
-        <v>98974</v>
+        <v>57861</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4560,10 +4509,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633706</v>
+        <v>633695</v>
       </c>
       <c r="R38" t="n">
-        <v>6658752</v>
+        <v>6658733</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4595,7 +4544,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4605,12 +4554,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4637,7 +4581,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130352568</v>
+        <v>130344259</v>
       </c>
       <c r="B39" t="n">
         <v>98974</v>
@@ -4667,7 +4611,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4681,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633653</v>
+        <v>633692</v>
       </c>
       <c r="R39" t="n">
-        <v>6658661</v>
+        <v>6658641</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,7 +4660,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4726,7 +4670,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,19 +4690,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130352572</v>
+        <v>130344251</v>
       </c>
       <c r="B40" t="n">
         <v>98974</v>
@@ -4783,7 +4732,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4793,14 +4742,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633680</v>
+        <v>633706</v>
       </c>
       <c r="R40" t="n">
-        <v>6658562</v>
+        <v>6658752</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4832,7 +4781,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4842,7 +4791,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4857,50 +4811,54 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130344249</v>
+        <v>130352568</v>
       </c>
       <c r="B41" t="n">
-        <v>57861</v>
+        <v>98974</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4909,10 +4867,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>633697</v>
+        <v>633653</v>
       </c>
       <c r="R41" t="n">
-        <v>6658765</v>
+        <v>6658661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4944,7 +4902,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4954,7 +4912,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4969,62 +4927,66 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130344260</v>
+        <v>130352572</v>
       </c>
       <c r="B42" t="n">
-        <v>57861</v>
+        <v>98974</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>633698</v>
+        <v>633680</v>
       </c>
       <c r="R42" t="n">
-        <v>6658625</v>
+        <v>6658562</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5056,7 +5018,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5066,7 +5028,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5081,60 +5043,65 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130354994</v>
+        <v>130344249</v>
       </c>
       <c r="B43" t="n">
-        <v>98988</v>
+        <v>57861</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gölinge, öster om, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>633691</v>
+        <v>633697</v>
       </c>
       <c r="R43" t="n">
-        <v>6658630</v>
+        <v>6658765</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5161,9 +5128,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5178,22 +5155,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130354986</v>
+        <v>130344260</v>
       </c>
       <c r="B44" t="n">
-        <v>97229</v>
+        <v>57861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5201,37 +5178,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gölinge, öster om, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633690</v>
+        <v>633698</v>
       </c>
       <c r="R44" t="n">
-        <v>6658637</v>
+        <v>6658625</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5258,9 +5240,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5275,15 +5267,209 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130354994</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98988</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gölinge, öster om, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>633691</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6658630</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
           <t>Vilhelm Kroon</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>Vilhelm Kroon</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130354986</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97229</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>53</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gölinge, öster om, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>633690</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6658637</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62003-2025 artfynd.xlsx
+++ b/artfynd/A 62003-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126653720</v>
+        <v>130140292</v>
       </c>
       <c r="B2" t="n">
-        <v>8798</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,58 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100808</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart ögonknäppare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Denticollis borealis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Paykull, 1800)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633536</v>
+        <v>633626</v>
       </c>
       <c r="R2" t="n">
-        <v>6658873</v>
+        <v>6658697</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +735,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>IBL1521</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,29 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans-Erik Wanntorp</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joachim Strengbom</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126653797</v>
+        <v>130354986</v>
       </c>
       <c r="B3" t="n">
-        <v>6726</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,53 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102354</v>
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Triplax rufipes</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Gölinge, öster om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633536</v>
+        <v>633690</v>
       </c>
       <c r="R3" t="n">
-        <v>6658873</v>
+        <v>6658637</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,17 +832,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,51 +851,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans-Erik Wanntorp</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joachim Strengbom</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130140331</v>
+        <v>130140296</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633693</v>
+        <v>633716</v>
       </c>
       <c r="R4" t="n">
-        <v>6658640</v>
+        <v>6658639</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -984,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 buketter 1316</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130140320</v>
+        <v>130140309</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633693</v>
+        <v>633716</v>
       </c>
       <c r="R5" t="n">
-        <v>6658694</v>
+        <v>6658639</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>8 buketter 1345</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130140317</v>
+        <v>130140295</v>
       </c>
       <c r="B6" t="n">
-        <v>97815</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,19 +1074,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221944</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1148,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633634</v>
+        <v>633745</v>
       </c>
       <c r="R6" t="n">
-        <v>6658696</v>
+        <v>6658775</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130140318</v>
+        <v>130140303</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633681</v>
+        <v>633595</v>
       </c>
       <c r="R7" t="n">
-        <v>6658735</v>
+        <v>6658626</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1281,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>9 buketter 1252</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130140309</v>
+        <v>130140307</v>
       </c>
       <c r="B8" t="n">
-        <v>92211</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633716</v>
+        <v>633545</v>
       </c>
       <c r="R8" t="n">
-        <v>6658639</v>
+        <v>6658735</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1372,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1409,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130140296</v>
+        <v>130294380</v>
       </c>
       <c r="B9" t="n">
-        <v>91758</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633716</v>
+        <v>633664</v>
       </c>
       <c r="R9" t="n">
-        <v>6658639</v>
+        <v>6658700</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1474,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130140327</v>
+        <v>130294381</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633701</v>
+        <v>633661</v>
       </c>
       <c r="R10" t="n">
-        <v>6658658</v>
+        <v>6658817</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1571,17 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4 buketter 1318</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,42 +1548,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130344257</v>
+        <v>130344249</v>
       </c>
       <c r="B11" t="n">
-        <v>98974</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1652,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633672</v>
+        <v>633697</v>
       </c>
       <c r="R11" t="n">
-        <v>6658700</v>
+        <v>6658765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,7 +1623,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1697,12 +1633,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,48 +1660,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130140325</v>
+        <v>130344254</v>
       </c>
       <c r="B12" t="n">
-        <v>98950</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633718</v>
+        <v>633695</v>
       </c>
       <c r="R12" t="n">
-        <v>6658738</v>
+        <v>6658733</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,17 +1730,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>5 buketter 1244</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,60 +1760,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130140298</v>
+        <v>130344260</v>
       </c>
       <c r="B13" t="n">
-        <v>58011</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633710</v>
+        <v>633698</v>
       </c>
       <c r="R13" t="n">
-        <v>6658772</v>
+        <v>6658625</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1896,12 +1842,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,60 +1872,81 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130140340</v>
+        <v>126653720</v>
       </c>
       <c r="B14" t="n">
-        <v>98950</v>
+        <v>8806</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100808</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart ögonknäppare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Denticollis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Paykull, 1800)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633707</v>
+        <v>633536</v>
       </c>
       <c r="R14" t="n">
-        <v>6658726</v>
+        <v>6658873</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1988,22 +1965,22 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>10 buketter 1247</t>
+          <t>IBL1521</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,50 +1989,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hans-Erik Wanntorp</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Joachim Strengbom</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130140343</v>
+        <v>130294384</v>
       </c>
       <c r="B15" t="n">
-        <v>98950</v>
+        <v>4781</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633719</v>
+        <v>633647</v>
       </c>
       <c r="R15" t="n">
-        <v>6658699</v>
+        <v>6658734</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2095,17 +2073,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 bukett 1301</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,10 +2110,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130140315</v>
+        <v>130354997</v>
       </c>
       <c r="B16" t="n">
-        <v>97821</v>
+        <v>4781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,34 +2121,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Gölinge, öster om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633550</v>
+        <v>633732</v>
       </c>
       <c r="R16" t="n">
-        <v>6658729</v>
+        <v>6658572</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2197,12 +2175,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2217,22 +2195,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130140292</v>
+        <v>130140298</v>
       </c>
       <c r="B17" t="n">
-        <v>97196</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,21 +2218,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2264,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633626</v>
+        <v>633710</v>
       </c>
       <c r="R17" t="n">
-        <v>6658697</v>
+        <v>6658772</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2326,10 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130140344</v>
+        <v>130140318</v>
       </c>
       <c r="B18" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633720</v>
+        <v>633681</v>
       </c>
       <c r="R18" t="n">
-        <v>6658686</v>
+        <v>6658735</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2401,7 +2379,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bukett 1301</t>
+          <t>9 buketter 1252</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2428,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130140339</v>
+        <v>130140320</v>
       </c>
       <c r="B19" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2463,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633700</v>
+        <v>633693</v>
       </c>
       <c r="R19" t="n">
-        <v>6658589</v>
+        <v>6658694</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2503,7 +2481,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>10 buketter 1310</t>
+          <t>8 buketter 1345</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2530,32 +2508,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130140312</v>
+        <v>130140322</v>
       </c>
       <c r="B20" t="n">
-        <v>97821</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2543,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633608</v>
+        <v>633712</v>
       </c>
       <c r="R20" t="n">
-        <v>6658722</v>
+        <v>6658740</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2601,6 +2579,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>7 buketter 1242</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,10 +2610,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130140336</v>
+        <v>130140325</v>
       </c>
       <c r="B21" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633697</v>
+        <v>633718</v>
       </c>
       <c r="R21" t="n">
-        <v>6658591</v>
+        <v>6658738</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2702,7 +2685,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>15 buketter 1309</t>
+          <t>5 buketter 1244</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2729,10 +2712,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130140322</v>
+        <v>130140327</v>
       </c>
       <c r="B22" t="n">
-        <v>98950</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2764,10 +2747,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633712</v>
+        <v>633701</v>
       </c>
       <c r="R22" t="n">
-        <v>6658740</v>
+        <v>6658658</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2804,7 +2787,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>7 buketter 1242</t>
+          <t>4 buketter 1318</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2831,44 +2814,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130140316</v>
+        <v>130344257</v>
       </c>
       <c r="B23" t="n">
-        <v>97815</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gölinge, Upl</t>
+          <t>Enbärsmossarna, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633655</v>
+        <v>633672</v>
       </c>
       <c r="R23" t="n">
-        <v>6658641</v>
+        <v>6658700</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2892,12 +2888,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2912,44 +2923,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130140303</v>
+        <v>130140331</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633595</v>
+        <v>633693</v>
       </c>
       <c r="R24" t="n">
-        <v>6658626</v>
+        <v>6658640</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2995,6 +3006,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3 buketter 1316</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,32 +3037,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130140307</v>
+        <v>130140336</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3072,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633545</v>
+        <v>633697</v>
       </c>
       <c r="R25" t="n">
-        <v>6658735</v>
+        <v>6658591</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3081,7 +3097,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3092,6 +3108,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>15 buketter 1309</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3118,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130294382</v>
+        <v>130140339</v>
       </c>
       <c r="B26" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,10 +3174,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633614</v>
+        <v>633700</v>
       </c>
       <c r="R26" t="n">
-        <v>6658718</v>
+        <v>6658589</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3183,17 +3204,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>6 buketter</t>
+          <t>10 buketter 1310</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3220,32 +3241,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130294380</v>
+        <v>130140340</v>
       </c>
       <c r="B27" t="n">
-        <v>57861</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3255,10 +3276,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633664</v>
+        <v>633707</v>
       </c>
       <c r="R27" t="n">
-        <v>6658700</v>
+        <v>6658726</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3285,12 +3306,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>10 buketter 1247</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3317,32 +3343,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130294381</v>
+        <v>130140343</v>
       </c>
       <c r="B28" t="n">
-        <v>57861</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3352,10 +3378,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>633661</v>
+        <v>633719</v>
       </c>
       <c r="R28" t="n">
-        <v>6658817</v>
+        <v>6658699</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3382,12 +3408,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3414,32 +3445,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130294384</v>
+        <v>130140344</v>
       </c>
       <c r="B29" t="n">
-        <v>4779</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3449,10 +3480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>633647</v>
+        <v>633720</v>
       </c>
       <c r="R29" t="n">
-        <v>6658734</v>
+        <v>6658686</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3479,17 +3510,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>1 bukett 1301</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3516,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130352567</v>
+        <v>130294382</v>
       </c>
       <c r="B30" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3544,29 +3575,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>633640</v>
+        <v>633614</v>
       </c>
       <c r="R30" t="n">
-        <v>6658662</v>
+        <v>6658718</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3590,22 +3612,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3620,22 +3637,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130344256</v>
+        <v>130344251</v>
       </c>
       <c r="B31" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3662,7 +3679,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3676,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633669</v>
+        <v>633706</v>
       </c>
       <c r="R31" t="n">
-        <v>6658717</v>
+        <v>6658752</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3711,7 +3728,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3721,7 +3738,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3753,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130352566</v>
+        <v>130344252</v>
       </c>
       <c r="B32" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3783,7 +3800,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3797,10 +3814,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>633645</v>
+        <v>633696</v>
       </c>
       <c r="R32" t="n">
-        <v>6658739</v>
+        <v>6658741</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,7 +3849,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3842,7 +3859,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3857,22 +3879,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130352569</v>
+        <v>130344255</v>
       </c>
       <c r="B33" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3899,7 +3921,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3913,10 +3935,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>633693</v>
+        <v>633703</v>
       </c>
       <c r="R33" t="n">
-        <v>6658643</v>
+        <v>6658736</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,7 +3970,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3958,7 +3980,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>skott</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3973,22 +4000,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130344255</v>
+        <v>130344256</v>
       </c>
       <c r="B34" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4015,7 +4042,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4029,10 +4056,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>633703</v>
+        <v>633669</v>
       </c>
       <c r="R34" t="n">
-        <v>6658736</v>
+        <v>6658717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4064,7 +4091,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4074,7 +4101,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4106,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130344252</v>
+        <v>130344259</v>
       </c>
       <c r="B35" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4136,7 +4163,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4150,10 +4177,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>633696</v>
+        <v>633692</v>
       </c>
       <c r="R35" t="n">
-        <v>6658741</v>
+        <v>6658641</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4185,7 +4212,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4195,7 +4222,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4230,7 +4257,7 @@
         <v>130344261</v>
       </c>
       <c r="B36" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4351,7 +4378,7 @@
         <v>130344262</v>
       </c>
       <c r="B37" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4469,38 +4496,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130344254</v>
+        <v>130352566</v>
       </c>
       <c r="B38" t="n">
-        <v>57861</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4509,10 +4540,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>633695</v>
+        <v>633645</v>
       </c>
       <c r="R38" t="n">
-        <v>6658733</v>
+        <v>6658739</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4544,7 +4575,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4554,7 +4585,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4569,22 +4600,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130344259</v>
+        <v>130352567</v>
       </c>
       <c r="B39" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4611,7 +4642,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4625,10 +4656,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>633692</v>
+        <v>633640</v>
       </c>
       <c r="R39" t="n">
-        <v>6658641</v>
+        <v>6658662</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4660,7 +4691,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4670,12 +4701,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4690,22 +4716,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130344251</v>
+        <v>130352568</v>
       </c>
       <c r="B40" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4732,7 +4758,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4746,10 +4772,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>633706</v>
+        <v>633653</v>
       </c>
       <c r="R40" t="n">
-        <v>6658752</v>
+        <v>6658661</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4781,7 +4807,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4791,12 +4817,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>skott</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4811,22 +4832,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130352568</v>
+        <v>130352569</v>
       </c>
       <c r="B41" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,7 +4874,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4867,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>633653</v>
+        <v>633693</v>
       </c>
       <c r="R41" t="n">
-        <v>6658661</v>
+        <v>6658643</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4902,7 +4923,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4912,7 +4933,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4942,7 +4963,7 @@
         <v>130352572</v>
       </c>
       <c r="B42" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5055,53 +5076,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130344249</v>
+        <v>130354994</v>
       </c>
       <c r="B43" t="n">
-        <v>57861</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, öster om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>633697</v>
+        <v>633691</v>
       </c>
       <c r="R43" t="n">
-        <v>6658765</v>
+        <v>6658630</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5128,19 +5144,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5155,65 +5161,56 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130344260</v>
+        <v>130140316</v>
       </c>
       <c r="B44" t="n">
-        <v>57861</v>
+        <v>97977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>221944</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Enbärsmossarna, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>633698</v>
+        <v>633655</v>
       </c>
       <c r="R44" t="n">
-        <v>6658625</v>
+        <v>6658641</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5237,22 +5234,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5267,57 +5254,53 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130354994</v>
+        <v>130140317</v>
       </c>
       <c r="B45" t="n">
-        <v>98988</v>
+        <v>97977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221944</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gölinge, öster om, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>633691</v>
+        <v>633634</v>
       </c>
       <c r="R45" t="n">
-        <v>6658630</v>
+        <v>6658696</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5344,12 +5327,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5364,57 +5347,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130354986</v>
+        <v>130140312</v>
       </c>
       <c r="B46" t="n">
-        <v>97229</v>
+        <v>97983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gölinge, öster om, Upl</t>
+          <t>Gölinge, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>633690</v>
+        <v>633608</v>
       </c>
       <c r="R46" t="n">
-        <v>6658637</v>
+        <v>6658722</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5441,12 +5424,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5461,15 +5444,112 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130140315</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gölinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>633550</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6658729</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
